--- a/example_files/west_nile_metadata.xlsx
+++ b/example_files/west_nile_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chachen/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mverbies/projects/dev_example_data/example_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54EFCDCE-4000-BF43-987D-A40408C41EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2765E1B6-6FED-E042-8285-3A6D5F3A1E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{8AA6C4E1-612A-6248-8120-629076D7CFF1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>submissionId</t>
   </si>
@@ -208,9 +208,6 @@
     <t>tissue</t>
   </si>
   <si>
-    <t>test_WNV-1/Cyanocitta cristata /USA/03003243/2003</t>
-  </si>
-  <si>
     <t>KX547593</t>
   </si>
   <si>
@@ -278,6 +275,27 @@
   </si>
   <si>
     <t>Glendale</t>
+  </si>
+  <si>
+    <t>test_WNV-1/Cyanocitta_cristata/USA/03003243/2003</t>
+  </si>
+  <si>
+    <t>sequencingInstrument</t>
+  </si>
+  <si>
+    <t>ILLUMINA</t>
+  </si>
+  <si>
+    <t>PacBio RS</t>
+  </si>
+  <si>
+    <t>files.rawReads</t>
+  </si>
+  <si>
+    <t>raw_reads_1.fq.gz</t>
+  </si>
+  <si>
+    <t>raw_reads_contaminated.fq.gz</t>
   </si>
 </sst>
 </file>
@@ -1139,10 +1157,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC5AC95-285D-7643-A533-C3A9B14982C8}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1182,8 +1205,14 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O1" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1211,8 +1240,14 @@
       <c r="M2" s="1">
         <v>40742</v>
       </c>
+      <c r="N2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O2" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1249,8 +1284,14 @@
       <c r="M3" s="1">
         <v>40367</v>
       </c>
+      <c r="N3" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1288,7 +1329,7 @@
         <v>42548</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1326,7 +1367,7 @@
         <v>41506</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1364,7 +1405,7 @@
         <v>42933</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -1402,7 +1443,7 @@
         <v>41943</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>56</v>
       </c>
@@ -1440,47 +1481,47 @@
         <v>39709</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>63</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" t="s">
         <v>68</v>
-      </c>
-      <c r="K9" t="s">
-        <v>69</v>
       </c>
       <c r="M9" s="1">
         <v>37892</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
         <v>70</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
@@ -1489,7 +1530,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
@@ -1501,7 +1542,7 @@
         <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
@@ -1513,21 +1554,21 @@
         <v>40402</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
@@ -1539,7 +1580,7 @@
         <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
@@ -1551,33 +1592,33 @@
         <v>42201</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>82</v>
-      </c>
-      <c r="F12" t="s">
-        <v>83</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s">
         <v>28</v>
